--- a/Unity/Assets/Config/Excel/Datas/__beans__.xlsx
+++ b/Unity/Assets/Config/Excel/Datas/__beans__.xlsx
@@ -15,12 +15,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>##var</t>
   </si>
@@ -76,47 +76,174 @@
     <t>注释</t>
   </si>
   <si>
+    <t>ALocalizeConfig</t>
+  </si>
+  <si>
+    <t>key</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>LocalizeConfig_CHS</t>
+  </si>
+  <si>
+    <t>TextCHS</t>
+  </si>
+  <si>
+    <t>LocalizeConfig_CHT</t>
+  </si>
+  <si>
+    <t>TextCHT</t>
+  </si>
+  <si>
     <t>LocalizeConfig_EN</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>ALocalizeConfig</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>key</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>LocalizeConfig_CHS</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>LocalizeConfig_CHT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TextCHS</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TextCHT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>TextEN</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ActionEventBaseData</t>
+  </si>
+  <si>
+    <t>battle action event base bean</t>
+  </si>
+  <si>
+    <t>RangeDamageActionEventData</t>
+  </si>
+  <si>
+    <t>,</t>
+  </si>
+  <si>
+    <t>range</t>
+  </si>
+  <si>
+    <t>range damage event bean</t>
+  </si>
+  <si>
+    <t>Radius</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>range radius in millimeters</t>
+  </si>
+  <si>
+    <t>BulletActionEventData</t>
+  </si>
+  <si>
+    <t>bullet</t>
+  </si>
+  <si>
+    <t>projectile event bean</t>
+  </si>
+  <si>
+    <t>BulletConfigId</t>
+  </si>
+  <si>
+    <t>bullet config id</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>speed in millimeters per second</t>
+  </si>
+  <si>
+    <t>LifeMs</t>
+  </si>
+  <si>
+    <t>life time in milliseconds</t>
+  </si>
+  <si>
+    <t>collision radius in millimeters</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>projectile count</t>
+  </si>
+  <si>
+    <t>SpreadAngleDeg</t>
+  </si>
+  <si>
+    <t>total spread angle in degrees</t>
+  </si>
+  <si>
+    <t>HitActionEventIds</t>
+  </si>
+  <si>
+    <t>(list#sep=|),int</t>
+  </si>
+  <si>
+    <t>on hit action event ids</t>
+  </si>
+  <si>
+    <t>AddBuffActionEventData</t>
+  </si>
+  <si>
+    <t>addbuff</t>
+  </si>
+  <si>
+    <t>add buff event bean</t>
+  </si>
+  <si>
+    <t>BuffId</t>
+  </si>
+  <si>
+    <t>buff config id</t>
+  </si>
+  <si>
+    <t>TargetRule</t>
+  </si>
+  <si>
+    <t>target rule</t>
+  </si>
+  <si>
+    <t>RemoveBuffActionEventData</t>
+  </si>
+  <si>
+    <t>removebuff</t>
+  </si>
+  <si>
+    <t>remove buff event bean</t>
+  </si>
+  <si>
+    <t>ChangeNumericActionEventData</t>
+  </si>
+  <si>
+    <t>changenumeric</t>
+  </si>
+  <si>
+    <t>change numeric event bean</t>
+  </si>
+  <si>
+    <t>NumericType</t>
+  </si>
+  <si>
+    <t>numeric type</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>delta value</t>
+  </si>
+  <si>
+    <t>InterruptLevel</t>
+  </si>
+  <si>
+    <t>interrupt level</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -156,13 +283,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -197,27 +317,27 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="1" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="3" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="4" applyFont="1" fillId="0" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" applyNumberFormat="1" fontId="2" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="2" applyProtection="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -497,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="3" width="20.6640625" customWidth="1"/>
@@ -507,26 +627,26 @@
     <col min="10" max="10" width="10.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="0" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="4" t="s">
@@ -537,163 +657,400 @@
       <c r="K1" s="4"/>
       <c r="L1" s="4"/>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="0" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="0" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
-      <c r="A3" t="s">
+    <row r="3">
+      <c r="A3" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="0" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="0" t="s">
         <v>16</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="0" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4">
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="H4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="K4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="B5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K4" s="2"/>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="B5" s="2" t="s">
+      <c r="C5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6">
       <c r="B6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="B10" s="2"/>
-    </row>
-    <row r="13" spans="1:12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8" s="0" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="I9" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K9" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="H10" s="0" t="s">
+        <v>39</v>
+      </c>
+      <c r="I10" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K10" s="0" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K11" s="0" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" s="0" t="s">
+        <v>43</v>
+      </c>
+      <c r="I12" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K12" s="0" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="H13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-    </row>
-    <row r="14" spans="1:12">
+      <c r="K13" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+      <c r="H14" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-    </row>
-    <row r="15" spans="1:12">
+      <c r="K14" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+      <c r="H15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>34</v>
+      </c>
       <c r="J15" s="3"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:12">
+      <c r="K15" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="H16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+      <c r="K16" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="0" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="0" t="s">
+        <v>55</v>
+      </c>
+      <c r="H17" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K17" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K18" s="0" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="0" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="0" t="s">
+        <v>62</v>
+      </c>
+      <c r="H19" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K19" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K20" s="0" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="0" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="F21" s="0" t="s">
+        <v>65</v>
+      </c>
+      <c r="H21" s="0" t="s">
+        <v>66</v>
+      </c>
+      <c r="I21" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K21" s="0" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="H22" s="0" t="s">
+        <v>68</v>
+      </c>
+      <c r="I22" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="0" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="H23" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K23" s="0" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="H24" s="0" t="s">
+        <v>70</v>
+      </c>
+      <c r="I24" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="K24" s="0" t="s">
+        <v>71</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells>
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>